--- a/outils/import-constats-excel/Gabarit/gabarit-constats-bsi.xlsx
+++ b/outils/import-constats-excel/Gabarit/gabarit-constats-bsi.xlsx
@@ -126,12 +126,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <cols>
-    <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="3" width="46" customWidth="1"/>
-    <col min="4" max="6" width="14" customWidth="1"/>
-    <col min="7" max="9" width="26" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
